--- a/scripts/ops-seed/carres-sku-master.xlsx
+++ b/scripts/ops-seed/carres-sku-master.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Laveo" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="NB Furniture" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Nice Future" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="HoOKkA" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Ohana" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Red Sofa" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Without Supplier Code " sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
